--- a/tests/fixtures/invoices.xlsx
+++ b/tests/fixtures/invoices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jsix/GIT_REPOS/FRUCHTiii/bikeworks-termin-planer/tests/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D171BAC5-5C16-0C4C-8B58-ECDBDBA499BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59131D17-0F45-7249-B935-4A0FC3A4B3AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="30240" windowHeight="20180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="18">
   <si>
     <t>Rechnungen</t>
   </si>
@@ -64,6 +64,21 @@
   </si>
   <si>
     <t>Test User</t>
+  </si>
+  <si>
+    <t>p1</t>
+  </si>
+  <si>
+    <t>p2</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>p3</t>
+  </si>
+  <si>
+    <t>p4</t>
   </si>
 </sst>
 </file>
@@ -132,9 +147,9 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -336,720 +351,730 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3">
         <v>27</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4">
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3">
         <v>194.49</v>
       </c>
-      <c r="J3" s="4"/>
+      <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3">
         <v>35</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="4">
+      <c r="C4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="3">
         <v>20020</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3">
         <v>67.900000000000006</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3">
         <v>67</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="4">
+      <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="3">
         <v>20080</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4">
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3">
         <v>72.239999999999995</v>
       </c>
-      <c r="J5" s="4"/>
+      <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3">
         <v>79</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="4">
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="3">
         <v>20046</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3">
         <v>204.45</v>
       </c>
-      <c r="J6" s="4"/>
+      <c r="J6" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3">
         <v>109</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="4">
+      <c r="C7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="3">
         <v>20065</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4">
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3">
         <v>172.32</v>
       </c>
-      <c r="J7" s="4"/>
+      <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3">
         <v>112</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="4">
+      <c r="C8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="3">
         <v>20067</v>
       </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4">
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3">
         <v>339.91</v>
       </c>
-      <c r="J8" s="4"/>
+      <c r="J8" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="9" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3">
         <v>113</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="4">
+      <c r="C9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="3">
         <v>20068</v>
       </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4">
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3">
         <v>10</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3">
         <v>128</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="4">
+      <c r="C10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="3">
         <v>20076</v>
       </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4">
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3">
         <v>1705.14</v>
       </c>
-      <c r="J10" s="4"/>
+      <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3">
         <v>132</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="4">
+      <c r="C11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="3">
         <v>20079</v>
       </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4">
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3">
         <v>0</v>
       </c>
-      <c r="J11" s="4"/>
+      <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3">
         <v>134</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4">
+      <c r="C12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3">
         <v>147</v>
       </c>
-      <c r="J12" s="4"/>
+      <c r="J12" s="3"/>
     </row>
     <row r="13" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3">
         <v>136</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="4">
+      <c r="C13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="3">
         <v>20081</v>
       </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4">
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3">
         <v>179.86</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3">
         <v>147</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="4">
+      <c r="C14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="3">
         <v>20089</v>
       </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4">
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3">
         <v>186.85</v>
       </c>
-      <c r="J14" s="4"/>
+      <c r="J14" s="3"/>
     </row>
     <row r="15" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3">
         <v>148</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="4">
+      <c r="C15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="3">
         <v>20090</v>
       </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4">
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3">
         <v>120.9</v>
       </c>
-      <c r="J15" s="4"/>
+      <c r="J15" s="3"/>
     </row>
     <row r="16" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3">
         <v>150</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="4">
+      <c r="C16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="3">
         <v>20092</v>
       </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4">
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3">
         <v>0</v>
       </c>
-      <c r="J16" s="4">
+      <c r="J16" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3">
         <v>152</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="4">
+      <c r="C17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3">
         <v>20093</v>
       </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4">
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3">
         <v>248.79</v>
       </c>
-      <c r="J17" s="4"/>
+      <c r="J17" s="3"/>
     </row>
     <row r="18" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3">
         <v>157</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="4">
+      <c r="C18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="3">
         <v>20098</v>
       </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4">
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3">
         <v>87.82</v>
       </c>
-      <c r="J18" s="4"/>
+      <c r="J18" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="19" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3">
         <v>159</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="4">
+      <c r="C19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="3">
         <v>20099</v>
       </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4">
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3">
         <v>0</v>
       </c>
-      <c r="J19" s="4">
+      <c r="J19" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3">
         <v>160</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="4">
+      <c r="C20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="3">
         <v>20100</v>
       </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4">
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3">
         <v>35.9</v>
       </c>
-      <c r="J20" s="4"/>
+      <c r="J20" s="3"/>
     </row>
     <row r="21" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3">
         <v>164</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="4">
+      <c r="C21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="3">
         <v>20095</v>
       </c>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4">
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3">
         <v>30.95</v>
       </c>
-      <c r="J21" s="4"/>
+      <c r="J21" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="22" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3">
         <v>168</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="4">
+      <c r="C22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="3">
         <v>20107</v>
       </c>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4">
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3">
         <v>60</v>
       </c>
-      <c r="J22" s="4"/>
+      <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3">
         <v>171</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="4">
+      <c r="C23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="3">
         <v>20110</v>
       </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4">
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3">
         <v>0</v>
       </c>
-      <c r="J23" s="4">
+      <c r="J23" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3">
         <v>172</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="4">
+      <c r="C24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="3">
         <v>20111</v>
       </c>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4">
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3">
         <v>54.98</v>
       </c>
-      <c r="J24" s="4"/>
+      <c r="J24" s="3"/>
     </row>
     <row r="25" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3">
         <v>173</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="4">
+      <c r="C25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="3">
         <v>20112</v>
       </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4">
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3">
         <v>161.41999999999999</v>
       </c>
-      <c r="J25" s="4"/>
+      <c r="J25" s="3"/>
     </row>
     <row r="26" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3">
         <v>177</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="4">
+      <c r="C26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="3">
         <v>20115</v>
       </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4">
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3">
         <v>90.84</v>
       </c>
-      <c r="J26" s="4">
+      <c r="J26" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3">
         <v>180</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" s="4">
+      <c r="C27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="3">
         <v>20117</v>
       </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4">
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3">
         <v>100.85</v>
       </c>
-      <c r="J27" s="4"/>
+      <c r="J27" s="3"/>
     </row>
     <row r="28" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3">
         <v>183</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="4">
+      <c r="C28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="3">
         <v>20072</v>
       </c>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4">
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3">
         <v>201.71</v>
       </c>
-      <c r="J28" s="4">
+      <c r="J28" s="3">
         <v>0.5</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3">
         <v>188</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="4">
+      <c r="C29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="3">
         <v>20120</v>
       </c>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4">
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3">
         <v>50</v>
       </c>
-      <c r="J29" s="4"/>
+      <c r="J29" s="3"/>
     </row>
     <row r="30" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3">
         <v>189</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="4">
+      <c r="C30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="3">
         <v>20121</v>
       </c>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4">
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3">
         <v>0</v>
       </c>
-      <c r="J30" s="4"/>
+      <c r="J30" s="3"/>
     </row>
     <row r="31" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3">
         <v>190</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="4">
+      <c r="C31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="3">
         <v>20085</v>
       </c>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4">
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3">
         <v>11.19</v>
       </c>
-      <c r="J31" s="4"/>
+      <c r="J31" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="32" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3">
         <v>192</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="4">
+      <c r="C32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="3">
         <v>20122</v>
       </c>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4">
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3">
         <v>65</v>
       </c>
-      <c r="J32" s="4"/>
+      <c r="J32" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
